--- a/Intersecciones/excels/AREQUIPA-ISLAY-MOLLENDO.xlsx
+++ b/Intersecciones/excels/AREQUIPA-ISLAY-MOLLENDO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-301988</t>
+          <t>I-199160</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-17.0248137</t>
+          <t>-17.0221147</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-72.0076271</t>
+          <t>-71.9990447</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru / Calle José Carlos Mariátegui</t>
+          <t>Calle 7 / Vía de Evitamiento</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -535,12 +535,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-302092</t>
+          <t>I-234730</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>040701</t>
+          <t>040702</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -555,22 +555,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MOLLENDO</t>
+          <t>COCACHACRA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-17.0248314</t>
+          <t>-17.103877</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-72.0075336</t>
+          <t>-71.7826006</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru / Calle José Carlos Mariátegui</t>
+          <t>Avenida Libertad / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -579,6 +579,1410 @@
         </is>
       </c>
       <c r="J3" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>I-585074</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-17.0235594</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-71.9973644</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>I-199098</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-17.018512</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-72.0139959</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Avenida Mariscal Castilla / Calle Teófilo Nuñez</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>I-463015</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>040702</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>COCACHACRA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-17.0749807</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-71.72237</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>I-370449</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>040702</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>COCACHACRA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-17.0816098</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-71.7569595</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>I-368187</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>040702</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>COCACHACRA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-16.9855666</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-71.6274265</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>I-368181</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>040702</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>COCACHACRA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-16.9871776</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-71.6317542</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I-368177</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>040702</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>COCACHACRA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-16.9864016</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-71.6305808</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>I-368164</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>040702</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>COCACHACRA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-17.0031541</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-71.6081602</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>I-368173</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>040702</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>COCACHACRA</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-16.9979172</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-71.6332506</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>I-196139</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-17.019211</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-72.006806</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Calle Francisco Bolognesi / Calle Francisco Pizarro</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>I-530006</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-16.7007716</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-71.9106303</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>I-558767</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-17.0276885</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-72.0173515</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Calle Dean Valdivia / Calle Iquitos</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>I-558766</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-17.026835</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-72.0186221</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Calle Islay / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>I-533354</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-16.7060254</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-71.9063815</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>I-533353</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-16.6918822</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-71.9012865</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>I-532756</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-16.6823475</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-71.9055152</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>I-532751</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-16.678469</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-71.9118901</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>I-532713</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-16.697737</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-71.8874834</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>I-530005</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-16.7013177</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-71.9118402</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>I-530002</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-16.699436</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-71.9097768</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>I-529998</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-16.700877</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-71.9090377</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>I-595187</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-17.0320218</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-72.0053238</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>I-595194</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-17.030397</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-72.0055689</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>I-595191</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-17.0323869</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-72.0078841</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>I-595190</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-17.0314483</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-72.0076347</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>I-595188</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-17.0304322</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-72.0038388</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>I-680283</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-16.6795285</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-71.9127012</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>040701</t>
         </is>

--- a/Intersecciones/excels/AREQUIPA-ISLAY-MOLLENDO.xlsx
+++ b/Intersecciones/excels/AREQUIPA-ISLAY-MOLLENDO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1988,6 +1988,370 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>I-196142</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-17.017372</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-72.0041553</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Calle Francisco Pizarro / Vía de Evitamiento</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>I-529991</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-16.6989783</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-71.9069659</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>I-558816</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-17.0050594</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-72.0311741</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>I-558814</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-17.0039245</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-72.0302733</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Carretera Matarani - Mollendo / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>I-558813</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-17.0102632</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-72.02343</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>I-368159</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>040702</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>COCACHACRA</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-17.0669477</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-71.7163192</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>I-368160</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>040702</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>COCACHACRA</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-17.0664276</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-71.7164195</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/AREQUIPA-ISLAY-MOLLENDO.xlsx
+++ b/Intersecciones/excels/AREQUIPA-ISLAY-MOLLENDO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Panamericana Norte / Calle s / n</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2347,6 +2347,110 @@
         </is>
       </c>
       <c r="J37" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>I-368172</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>040702</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>COCACHACRA</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-16.9845559</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-71.6275231</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>040701</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>I-368144</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>040702</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>COCACHACRA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-17.0105052</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-71.5590798</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>040701</t>
         </is>

--- a/Intersecciones/excels/AREQUIPA-ISLAY-MOLLENDO.xlsx
+++ b/Intersecciones/excels/AREQUIPA-ISLAY-MOLLENDO.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-199160</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-17.0221147</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-234730</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>040702</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>COCACHACRA</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-17.103877</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-585074</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-17.0235594</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-199098</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-17.018512</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-463015</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>040702</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>COCACHACRA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-17.0749807</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-370449</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>040702</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>COCACHACRA</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-17.0816098</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-368187</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>040702</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>COCACHACRA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-16.9855666</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-368181</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>040702</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>COCACHACRA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-16.9871776</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-368177</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>040702</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>COCACHACRA</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-16.9864016</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-368164</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>040702</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>COCACHACRA</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-17.0031541</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-368173</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>040702</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>COCACHACRA</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-16.9979172</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-196139</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-17.019211</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-530006</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-16.7007716</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-558767</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-17.0276885</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-558766</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-17.026835</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-533354</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-16.7060254</t>
@@ -1304,40 +1224,35 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>I-533353</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-16.6918822</t>
@@ -1356,40 +1271,35 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>I-532756</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-16.6823475</t>
@@ -1408,40 +1318,35 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>I-532751</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-16.678469</t>
@@ -1460,40 +1365,35 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>I-532713</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-16.697737</t>
@@ -1512,40 +1412,35 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>I-530005</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-16.7013177</t>
@@ -1564,40 +1459,35 @@
       <c r="I22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>I-530002</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-16.699436</t>
@@ -1616,40 +1506,35 @@
       <c r="I23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>I-529998</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-16.700877</t>
@@ -1668,40 +1553,35 @@
       <c r="I24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>I-595187</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-17.0320218</t>
@@ -1720,40 +1600,35 @@
       <c r="I25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>I-595194</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>-17.030397</t>
@@ -1772,40 +1647,35 @@
       <c r="I26" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>I-595191</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>-17.0323869</t>
@@ -1824,40 +1694,35 @@
       <c r="I27" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>I-595190</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>-17.0314483</t>
@@ -1876,40 +1741,35 @@
       <c r="I28" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>I-595188</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>-17.0304322</t>
@@ -1928,40 +1788,35 @@
       <c r="I29" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>I-680283</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>-16.6795285</t>
@@ -1980,40 +1835,35 @@
       <c r="I30" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>I-196142</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>-17.017372</t>
@@ -2032,40 +1882,35 @@
       <c r="I31" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>I-529991</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>-16.6989783</t>
@@ -2084,40 +1929,35 @@
       <c r="I32" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>I-558816</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>-17.0050594</t>
@@ -2136,40 +1976,35 @@
       <c r="I33" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>I-558814</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>-17.0039245</t>
@@ -2188,40 +2023,35 @@
       <c r="I34" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>I-558813</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>040701</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>MOLLENDO</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>-17.0102632</t>
@@ -2240,40 +2070,35 @@
       <c r="I35" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>I-368159</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>040702</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>COCACHACRA</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>-17.0669477</t>
@@ -2292,40 +2117,35 @@
       <c r="I36" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>I-368160</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>040702</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>COCACHACRA</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>-17.0664276</t>
@@ -2344,40 +2164,35 @@
       <c r="I37" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>I-368172</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>040702</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>COCACHACRA</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>-16.9845559</t>
@@ -2396,40 +2211,35 @@
       <c r="I38" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>040701</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ISLAY</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>MOLLENDO</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>I-368144</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>040702</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>ISLAY</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>COCACHACRA</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>-17.0105052</t>
@@ -2448,11 +2258,6 @@
       <c r="I39" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>040701</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/AREQUIPA-ISLAY-MOLLENDO.xlsx
+++ b/Intersecciones/excels/AREQUIPA-ISLAY-MOLLENDO.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/AREQUIPA-ISLAY-MOLLENDO.xlsx
+++ b/Intersecciones/excels/AREQUIPA-ISLAY-MOLLENDO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/AREQUIPA-ISLAY-MOLLENDO.xlsx
+++ b/Intersecciones/excels/AREQUIPA-ISLAY-MOLLENDO.xlsx
@@ -486,22 +486,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-199160</t>
+          <t>I-680283</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-17.0221147</t>
+          <t>-16.6795285</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-71.9990447</t>
+          <t>-71.9127012</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Calle 7 / Vía de Evitamiento</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -533,27 +533,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-234730</t>
+          <t>I-595194</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-17.103877</t>
+          <t>-17.030397</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-71.7826006</t>
+          <t>-72.0055689</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Libertad / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -580,17 +580,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-585074</t>
+          <t>I-595191</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-17.0235594</t>
+          <t>-17.0323869</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-71.9973644</t>
+          <t>-72.0078841</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-199098</t>
+          <t>I-595190</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-17.018512</t>
+          <t>-17.0314483</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-72.0139959</t>
+          <t>-72.0076347</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Mariscal Castilla / Calle Teófilo Nuñez</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -674,17 +674,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-463015</t>
+          <t>I-595188</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-17.0749807</t>
+          <t>-17.0304322</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-71.72237</t>
+          <t>-72.0038388</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -721,17 +721,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-370449</t>
+          <t>I-595187</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-17.0816098</t>
+          <t>-17.0320218</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-71.7569595</t>
+          <t>-72.0053238</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-368187</t>
+          <t>I-585074</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-16.9855666</t>
+          <t>-17.0235594</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-71.6274265</t>
+          <t>-71.9973644</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -815,17 +815,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-368181</t>
+          <t>I-558816</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-16.9871776</t>
+          <t>-17.0050594</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-71.6317542</t>
+          <t>-72.0311741</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -862,22 +862,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-368177</t>
+          <t>I-558814</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-16.9864016</t>
+          <t>-17.0039245</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-71.6305808</t>
+          <t>-72.0302733</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Carretera Matarani - Mollendo / Calle s / n</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -909,17 +909,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-368164</t>
+          <t>I-558813</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-17.0031541</t>
+          <t>-17.0102632</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-71.6081602</t>
+          <t>-72.02343</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-368173</t>
+          <t>I-558767</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-16.9979172</t>
+          <t>-17.0276885</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-71.6332506</t>
+          <t>-72.0173515</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Calle Dean Valdivia / Calle Iquitos</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1003,22 +1003,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-196139</t>
+          <t>I-558766</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-17.019211</t>
+          <t>-17.026835</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-72.006806</t>
+          <t>-72.0186221</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Calle Francisco Bolognesi / Calle Francisco Pizarro</t>
+          <t>Calle Islay / Calle s / n</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1050,17 +1050,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-530006</t>
+          <t>I-533354</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-16.7007716</t>
+          <t>-16.7060254</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-71.9106303</t>
+          <t>-71.9063815</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1097,22 +1097,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-558767</t>
+          <t>I-533353</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-17.0276885</t>
+          <t>-16.6918822</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-72.0173515</t>
+          <t>-71.9012865</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Calle Dean Valdivia / Calle Iquitos</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1144,22 +1144,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-558766</t>
+          <t>I-532756</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-17.026835</t>
+          <t>-16.6823475</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-72.0186221</t>
+          <t>-71.9055152</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Calle Islay / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1191,17 +1191,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-533354</t>
+          <t>I-532751</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-16.7060254</t>
+          <t>-16.678469</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-71.9063815</t>
+          <t>-71.9118901</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1238,17 +1238,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-533353</t>
+          <t>I-532713</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-16.6918822</t>
+          <t>-16.697737</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-71.9012865</t>
+          <t>-71.8874834</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I-532756</t>
+          <t>I-530006</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-16.6823475</t>
+          <t>-16.7007716</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-71.9055152</t>
+          <t>-71.9106303</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1332,17 +1332,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I-532751</t>
+          <t>I-530005</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-16.678469</t>
+          <t>-16.7013177</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-71.9118901</t>
+          <t>-71.9118402</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1379,17 +1379,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I-532713</t>
+          <t>I-530002</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-16.697737</t>
+          <t>-16.699436</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-71.8874834</t>
+          <t>-71.9097768</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I-530005</t>
+          <t>I-529998</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-16.7013177</t>
+          <t>-16.700877</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-71.9118402</t>
+          <t>-71.9090377</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I-530002</t>
+          <t>I-529991</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-16.699436</t>
+          <t>-16.6989783</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-71.9097768</t>
+          <t>-71.9069659</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1520,17 +1520,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I-529998</t>
+          <t>I-463015</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-16.700877</t>
+          <t>-17.0749807</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-71.9090377</t>
+          <t>-71.72237</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1567,17 +1567,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>I-595187</t>
+          <t>I-370449</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-17.0320218</t>
+          <t>-17.0816098</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-72.0053238</t>
+          <t>-71.7569595</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1614,17 +1614,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>I-595194</t>
+          <t>I-368187</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-17.030397</t>
+          <t>-16.9855666</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-72.0055689</t>
+          <t>-71.6274265</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>I-595191</t>
+          <t>I-368181</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-17.0323869</t>
+          <t>-16.9871776</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-72.0078841</t>
+          <t>-71.6317542</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1708,17 +1708,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>I-595190</t>
+          <t>I-368177</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-17.0314483</t>
+          <t>-16.9864016</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-72.0076347</t>
+          <t>-71.6305808</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1755,17 +1755,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>I-595188</t>
+          <t>I-368173</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-17.0304322</t>
+          <t>-16.9979172</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-72.0038388</t>
+          <t>-71.6332506</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1802,17 +1802,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>I-680283</t>
+          <t>I-368172</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-16.6795285</t>
+          <t>-16.9845559</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-71.9127012</t>
+          <t>-71.6275231</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1849,22 +1849,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>I-196142</t>
+          <t>I-368164</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-17.017372</t>
+          <t>-17.0031541</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-72.0041553</t>
+          <t>-71.6081602</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Calle Francisco Pizarro / Vía de Evitamiento</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1896,17 +1896,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>I-529991</t>
+          <t>I-368160</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-16.6989783</t>
+          <t>-17.0664276</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-71.9069659</t>
+          <t>-71.7164195</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1943,17 +1943,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>I-558816</t>
+          <t>I-368159</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-17.0050594</t>
+          <t>-17.0669477</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-72.0311741</t>
+          <t>-71.7163192</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1990,22 +1990,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>I-558814</t>
+          <t>I-368144</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-17.0039245</t>
+          <t>-17.0105052</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-72.0302733</t>
+          <t>-71.5590798</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Carretera Matarani - Mollendo / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2037,27 +2037,27 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>I-558813</t>
+          <t>I-234730</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-17.0102632</t>
+          <t>-17.103877</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-72.02343</t>
+          <t>-71.7826006</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Avenida Panamericana Norte / Calle s / n</t>
+          <t>Avenida Libertad / Calle s / n</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2084,22 +2084,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>I-368159</t>
+          <t>I-199160</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-17.0669477</t>
+          <t>-17.0221147</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-71.7163192</t>
+          <t>-71.9990447</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Calle 7 / Vía de Evitamiento</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2131,22 +2131,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>I-368160</t>
+          <t>I-199098</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-17.0664276</t>
+          <t>-17.018512</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-71.7164195</t>
+          <t>-72.0139959</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Mariscal Castilla / Calle Teófilo Nuñez</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2178,22 +2178,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>I-368172</t>
+          <t>I-196142</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-16.9845559</t>
+          <t>-17.017372</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-71.6275231</t>
+          <t>-72.0041553</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Calle Francisco Pizarro / Vía de Evitamiento</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2225,22 +2225,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>I-368144</t>
+          <t>I-196139</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-17.0105052</t>
+          <t>-17.019211</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-71.5590798</t>
+          <t>-72.006806</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Calle Francisco Bolognesi / Calle Francisco Pizarro</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
